--- a/data/outplant/baywater/outplant_metadata_baywater.xlsx
+++ b/data/outplant/baywater/outplant_metadata_baywater.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashuffmyer/MyProjects/oysters/polyIC-larvae/data/outplant/baywater/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339A9130-CC58-1E40-9131-970220855929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305DB5C1-2BD6-684D-B6F6-02C855F28C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="12320" windowHeight="17760" xr2:uid="{0DAF8851-3CE0-B641-BA5A-C7AC4208D2FB}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="16180" windowHeight="17760" xr2:uid="{0DAF8851-3CE0-B641-BA5A-C7AC4208D2FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="25">
   <si>
     <t>treatment</t>
   </si>
@@ -93,6 +93,24 @@
   </si>
   <si>
     <t>from health trays; source tag is purple tag from trays; new tags are yellow</t>
+  </si>
+  <si>
+    <t>20260606.notes</t>
+  </si>
+  <si>
+    <t>empty, removed from outplant</t>
+  </si>
+  <si>
+    <t>20260606.mortality</t>
+  </si>
+  <si>
+    <t>weird size variation, includes large and small oysters</t>
+  </si>
+  <si>
+    <t>weird size variation, includes large and small oysters; logger in bag</t>
+  </si>
+  <si>
+    <t>logger in bag</t>
   </si>
 </sst>
 </file>
@@ -464,20 +482,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDD65DDB-7482-D846-9B42-22485EDC3B2E}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="4" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="8" max="8" width="116.33203125" customWidth="1"/>
+    <col min="9" max="9" width="50.83203125" customWidth="1"/>
     <col min="10" max="10" width="21" customWidth="1"/>
     <col min="17" max="17" width="16.33203125" customWidth="1"/>
     <col min="18" max="18" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -502,8 +520,14 @@
       <c r="H1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -525,8 +549,14 @@
       <c r="H2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -548,8 +578,11 @@
       <c r="H3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -571,8 +604,14 @@
       <c r="H4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -594,8 +633,14 @@
       <c r="H5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -617,14 +662,23 @@
       <c r="H6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>34</v>
       </c>
       <c r="B7">
         <v>362</v>
       </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
@@ -634,14 +688,23 @@
       <c r="H7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>33</v>
       </c>
       <c r="B8">
         <v>363</v>
       </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
@@ -651,14 +714,20 @@
       <c r="H8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>60</v>
       </c>
       <c r="B9">
         <v>377</v>
       </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
@@ -671,14 +740,23 @@
       <c r="H9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>31</v>
       </c>
       <c r="B10">
         <v>378</v>
       </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
@@ -688,14 +766,20 @@
       <c r="H10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>39</v>
       </c>
       <c r="B11">
         <v>382</v>
       </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
@@ -705,14 +789,20 @@
       <c r="H11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>49</v>
       </c>
       <c r="B12">
         <v>381</v>
       </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
@@ -722,14 +812,23 @@
       <c r="H12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>40</v>
       </c>
       <c r="B13">
         <v>383</v>
       </c>
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
         <v>14</v>
       </c>
@@ -739,14 +838,23 @@
       <c r="H13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>50</v>
       </c>
       <c r="B14">
         <v>364</v>
       </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
       <c r="D14" t="s">
         <v>14</v>
       </c>
@@ -755,6 +863,12 @@
       </c>
       <c r="H14" t="s">
         <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
